--- a/src-tauri/samples/mame/13_mame_verdict.xlsx
+++ b/src-tauri/samples/mame/13_mame_verdict.xlsx
@@ -517,7 +517,7 @@
     <col width="26" customWidth="1" min="27" max="27"/>
     <col width="9" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="21" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="9" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
@@ -776,12 +776,12 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>T199C</t>
+          <t>T82G, T83C, C84G</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>Y67H</t>
+          <t>F28A</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>T299C</t>
+          <t>C232G, A233C</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>F100S</t>
+          <t>H78A</t>
         </is>
       </c>
       <c r="AF3" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>A442C, G443C</t>
+          <t>C263T</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>S148P</t>
+          <t>A88V</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>C445G</t>
+          <t>C289G, G290C</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>H149D</t>
+          <t>R97A</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>T461C</t>
+          <t>A370G, T371C</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>M154T</t>
+          <t>I124A</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>T491C</t>
+          <t>A448G, A449C</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>V164A</t>
+          <t>N150A</t>
         </is>
       </c>
       <c r="AF7" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>T503C</t>
+          <t>A487G, A488C</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>I168T</t>
+          <t>K163A</t>
         </is>
       </c>
       <c r="AF8" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>A610T, C611A</t>
+          <t>G524C, C525G</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>T204Y</t>
+          <t>G175A</t>
         </is>
       </c>
       <c r="AF9" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>T616A</t>
+          <t>G569C</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>S206T</t>
+          <t>G190A</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>G619A, C620A, C621G</t>
+          <t>C598G, A599C</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>A207K</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Y67H</t>
+          <t>F28A</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Y67H</t>
+          <t>F28A</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>F100S</t>
+          <t>H78A</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>F100S</t>
+          <t>H78A</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>S148P</t>
+          <t>A88V</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>S148P</t>
+          <t>A88V</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>H149D</t>
+          <t>R97A</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>H149D</t>
+          <t>R97A</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr"/>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>M154T</t>
+          <t>I124A</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>M154T</t>
+          <t>I124A</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>V164A</t>
+          <t>N150A</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>V164A</t>
+          <t>N150A</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>I168T</t>
+          <t>K163A</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>I168T</t>
+          <t>K163A</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr"/>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>T204Y</t>
+          <t>G175A</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>T204Y</t>
+          <t>G175A</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>S206T</t>
+          <t>G190A</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>S206T</t>
+          <t>G190A</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>A207K</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>A207K</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Y67H</t>
+          <t>F28A</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Y67H</t>
+          <t>F28A</t>
         </is>
       </c>
       <c r="G2" s="5" t="n">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>F100S</t>
+          <t>H78A</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>F100S</t>
+          <t>H78A</t>
         </is>
       </c>
       <c r="G3" s="7" t="n">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>S148P</t>
+          <t>A88V</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>S148P</t>
+          <t>A88V</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>H149D</t>
+          <t>R97A</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>H149D</t>
+          <t>R97A</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>M154T</t>
+          <t>I124A</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>M154T</t>
+          <t>I124A</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>V164A</t>
+          <t>N150A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>V164A</t>
+          <t>N150A</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>I168T</t>
+          <t>K163A</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>I168T</t>
+          <t>K163A</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>T204Y</t>
+          <t>G175A</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>T204Y</t>
+          <t>G175A</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>S206T</t>
+          <t>G190A</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>S206T</t>
+          <t>G190A</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>A207K</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>A207K</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Y67H</t>
+          <t>F28A</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>F100S</t>
+          <t>H78A</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>S148P</t>
+          <t>A88V</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>H149D</t>
+          <t>R97A</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>M154T</t>
+          <t>I124A</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>V164A</t>
+          <t>N150A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>I168T</t>
+          <t>K163A</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>T204Y</t>
+          <t>G175A</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>S206T</t>
+          <t>G190A</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>A207K</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T02:57:17Z</t>
+          <t>2026-08-27T07:42:54Z</t>
         </is>
       </c>
     </row>

--- a/src-tauri/samples/mame/13_mame_verdict.xlsx
+++ b/src-tauri/samples/mame/13_mame_verdict.xlsx
@@ -4062,100 +4062,96 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="2" t="n">
         <v>0.97</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="2" t="n">
         <v>334</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="2" t="n">
         <v>342</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="2" t="n">
         <v>334</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7" t="n">
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr"/>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="n">
+      <c r="M17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="n">
         <v>0.9584</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="T17" s="2" t="n">
         <v>334</v>
       </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="inlineStr"/>
-      <c r="W17" s="7" t="inlineStr"/>
-      <c r="X17" s="7" t="inlineStr"/>
-      <c r="Y17" s="7" t="inlineStr"/>
-      <c r="Z17" s="7" t="n">
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="n">
         <v>0.9313</v>
       </c>
-      <c r="AA17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="7" t="inlineStr"/>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AA17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>8_2</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
-        <is>
-          <t>A707C, G708C, A715G, A716C</t>
-        </is>
-      </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>E236A, K239A</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AG17" s="7" t="inlineStr">
-        <is>
-          <t>E236A within window(±5 codon of 239)</t>
-        </is>
-      </c>
-      <c r="AH17" s="7" t="inlineStr"/>
-      <c r="AI17" s="7" t="inlineStr"/>
-      <c r="AJ17" s="7" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>A715G, A716C</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>K239A</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5898,104 +5894,100 @@
       <c r="AJ16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="2" t="n">
         <v>0.97</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7" t="n">
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr"/>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="n">
+      <c r="M17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="n">
         <v>0.9788</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="T17" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="inlineStr"/>
-      <c r="W17" s="7" t="inlineStr"/>
-      <c r="X17" s="7" t="inlineStr"/>
-      <c r="Y17" s="7" t="inlineStr"/>
-      <c r="Z17" s="7" t="n">
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="n">
         <v>0.945</v>
       </c>
-      <c r="AA17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="7" t="inlineStr"/>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AA17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>8_2</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
-        <is>
-          <t>A707C, G708C, A715G, A716C</t>
-        </is>
-      </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>E236A, K239A</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AG17" s="7" t="inlineStr">
-        <is>
-          <t>E236A within window(±5 codon of 239)</t>
-        </is>
-      </c>
-      <c r="AH17" s="7" t="inlineStr">
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>A715G, A716C</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>K239A</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr"/>
-      <c r="AJ17" s="7" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -6884,21 +6876,17 @@
           <t>K239A</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>E236A within window(±5 codon of 239)</t>
-        </is>
-      </c>
+      <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>E236A, K239A</t>
+          <t>K239A</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
@@ -9581,7 +9569,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>E236A, K239A</t>
+          <t>K239A</t>
         </is>
       </c>
       <c r="J17" s="12" t="n">
@@ -9594,7 +9582,7 @@
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>E236A, K239A</t>
+          <t>K239A</t>
         </is>
       </c>
       <c r="M17" s="12" t="n">
@@ -10297,8 +10285,16 @@
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -10381,7 +10377,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>2026-08-31T01:20:33Z</t>
+          <t>2026-08-31T04:38:48Z</t>
         </is>
       </c>
     </row>

--- a/src-tauri/samples/mame/13_mame_verdict.xlsx
+++ b/src-tauri/samples/mame/13_mame_verdict.xlsx
@@ -77,6 +77,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
       </patternFill>
@@ -85,12 +91,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00DFE3E8"/>
         <bgColor rgb="00DFE3E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -554,13 +554,13 @@
     <col width="26" customWidth="1" min="27" max="27"/>
     <col width="46" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="46" customWidth="1" min="30" max="30"/>
-    <col width="42" customWidth="1" min="31" max="31"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="46" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="46" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>substitution support 0.705 below plate baseline 0.923 (MAD 0.021)</t>
+          <t>substitution support 0.705 below plate baseline 0.922 (MAD 0.019)</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
@@ -1598,100 +1598,96 @@
       <c r="AJ10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="2" t="n">
         <v>0.97</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="2" t="n">
         <v>238</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="n">
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="n">
+      <c r="M11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="n">
         <v>0.9657</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="n">
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="n">
         <v>0.9335</v>
       </c>
-      <c r="AA11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
+      <c r="AA11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>2_2</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>A599G</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr">
-        <is>
-          <t>H200R</t>
-        </is>
-      </c>
-      <c r="AF11" s="4" t="inlineStr">
-        <is>
-          <t>WRONG_AA</t>
-        </is>
-      </c>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t>expected H200A, observed H200R</t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>C598G, A599C</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>H200A</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1790,500 +1786,472 @@
       <c r="AJ12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="2" t="n">
         <v>0.97</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>208</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="C13" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5" t="inlineStr"/>
-      <c r="S13" s="5" t="n">
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="n">
         <v>0.9545</v>
       </c>
-      <c r="T13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="U13" s="5" t="inlineStr"/>
-      <c r="V13" s="5" t="inlineStr"/>
-      <c r="W13" s="5" t="inlineStr"/>
-      <c r="X13" s="5" t="inlineStr"/>
-      <c r="Y13" s="5" t="inlineStr"/>
-      <c r="Z13" s="5" t="n">
-        <v>0.9161</v>
-      </c>
-      <c r="AA13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="5" t="inlineStr"/>
-      <c r="AC13" s="5" t="inlineStr">
+      <c r="T13" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="n">
+        <v>0.9147</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>4_2</t>
         </is>
       </c>
-      <c r="AD13" s="5" t="inlineStr">
+      <c r="AD13" s="2" t="inlineStr">
         <is>
           <t>A628G, A629C</t>
         </is>
       </c>
-      <c r="AE13" s="5" t="inlineStr">
+      <c r="AE13" s="2" t="inlineStr">
         <is>
           <t>K210A</t>
         </is>
       </c>
-      <c r="AF13" s="5" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="AG13" s="5" t="inlineStr">
-        <is>
-          <t>mixed consensus signal: 1 positions, max_minor_allele_fraction=0.300</t>
-        </is>
-      </c>
-      <c r="AH13" s="5" t="inlineStr">
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>A643G, A644C</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>K215A</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AI13" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AJ13" s="5" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['MIXED']). Highest-volume NB01 (200 reads) used as fallback.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
         <v>0.97</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>221</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>229</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>221</v>
-      </c>
-      <c r="F14" s="4" t="n">
+      <c r="C15" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="n">
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="T14" s="4" t="n">
-        <v>221</v>
-      </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="AA14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>5_2</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>A625G, G626C, C634G, A643G, A644C, C652G, A653C, C661G, T662C, G663C, T670G, T671C</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t>S209A, P212A, K215A, H218A, L221A, F224A</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>MANY</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>observed 6 AA changes &gt; cutoff 5</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0.966</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="n">
+        <v>0.9417</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr"/>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="n">
+        <v>0.9059</v>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>C680T</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>A227V</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="n">
-        <v>0.9417</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="n">
-        <v>0.7020999999999999</v>
-      </c>
-      <c r="AA15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr">
-        <is>
-          <t>substitution support 0.702 below plate baseline 0.923 (MAD 0.021)</t>
-        </is>
-      </c>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>6_2</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>C680T</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr">
-        <is>
-          <t>A227V</t>
-        </is>
-      </c>
-      <c r="AF15" s="3" t="inlineStr">
-        <is>
-          <t>LOWDEPTH</t>
-        </is>
-      </c>
-      <c r="AG15" s="3" t="inlineStr">
-        <is>
-          <t>read_count=14 &lt; min_read_count=30</t>
-        </is>
-      </c>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="n">
+        <v>0.9442</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="n">
+        <v>0.9024</v>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>A704C</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>D235A</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
         <v>0.97</v>
       </c>
-      <c r="C16" s="6" t="n">
-        <v>194</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>202</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>194</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="C17" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>239</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6" t="n">
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="M16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="n">
-        <v>0.9442</v>
-      </c>
-      <c r="T16" s="6" t="n">
-        <v>194</v>
-      </c>
-      <c r="U16" s="6" t="inlineStr"/>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="6" t="inlineStr"/>
-      <c r="Y16" s="6" t="inlineStr"/>
-      <c r="Z16" s="6" t="n">
-        <v>0.9024</v>
-      </c>
-      <c r="AA16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="6" t="inlineStr"/>
-      <c r="AC16" s="6" t="inlineStr">
-        <is>
-          <t>7_2</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr">
-        <is>
-          <t>G4N, T5N, G6N, A7N, G8N, A704C</t>
-        </is>
-      </c>
-      <c r="AE16" s="6" t="inlineStr">
-        <is>
-          <t>D235A</t>
-        </is>
-      </c>
-      <c r="AF16" s="6" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AG16" s="6" t="inlineStr">
-        <is>
-          <t>consensus_n_fraction=0.007 &gt; max_consensus_n_fraction=0.000; no_call_aa=2</t>
-        </is>
-      </c>
-      <c r="AH16" s="6" t="inlineStr"/>
-      <c r="AI16" s="6" t="inlineStr"/>
-      <c r="AJ16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="C17" s="7" t="n">
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="T17" s="5" t="n">
         <v>231</v>
       </c>
-      <c r="D17" s="7" t="n">
-        <v>239</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>231</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr"/>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="n">
-        <v>0.9742</v>
-      </c>
-      <c r="T17" s="7" t="n">
-        <v>231</v>
-      </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="inlineStr"/>
-      <c r="W17" s="7" t="inlineStr"/>
-      <c r="X17" s="7" t="inlineStr"/>
-      <c r="Y17" s="7" t="inlineStr"/>
-      <c r="Z17" s="7" t="n">
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="Z17" s="5" t="n">
         <v>0.9447</v>
       </c>
-      <c r="AA17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="7" t="inlineStr"/>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AA17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="5" t="inlineStr"/>
+      <c r="AC17" s="5" t="inlineStr">
         <is>
           <t>8_2</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
+      <c r="AD17" s="5" t="inlineStr">
         <is>
           <t>A707C, G708C, A715G, A716C</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="inlineStr">
+      <c r="AE17" s="5" t="inlineStr">
         <is>
           <t>E236A, K239A</t>
         </is>
       </c>
-      <c r="AF17" s="7" t="inlineStr">
+      <c r="AF17" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AG17" s="7" t="inlineStr">
+      <c r="AG17" s="5" t="inlineStr">
         <is>
           <t>E236A within window(±5 codon of 239)</t>
         </is>
       </c>
-      <c r="AH17" s="7" t="inlineStr"/>
-      <c r="AI17" s="7" t="inlineStr"/>
-      <c r="AJ17" s="7" t="inlineStr"/>
+      <c r="AH17" s="5" t="inlineStr"/>
+      <c r="AI17" s="5" t="inlineStr"/>
+      <c r="AJ17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2408,15 +2376,15 @@
     <col width="20" customWidth="1" min="25" max="25"/>
     <col width="21" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
-    <col width="46" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="46" customWidth="1" min="30" max="30"/>
-    <col width="42" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
     <col width="46" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="46" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3525,541 +3493,485 @@
           <t>expected H200A, observed H200R</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="n">
+        <v>0.9617</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="n">
+        <v>0.9351</v>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>3_2</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>C613G, A614C</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>Q205A</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AI11" s="4" t="inlineStr">
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="6" t="n">
+        <v>0.9684</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="U13" s="6" t="inlineStr"/>
+      <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="6" t="inlineStr"/>
+      <c r="X13" s="6" t="inlineStr"/>
+      <c r="Y13" s="6" t="inlineStr"/>
+      <c r="Z13" s="6" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="AA13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="6" t="inlineStr"/>
+      <c r="AC13" s="6" t="inlineStr">
+        <is>
+          <t>4_2</t>
+        </is>
+      </c>
+      <c r="AD13" s="6" t="inlineStr">
+        <is>
+          <t>A628G, A629C</t>
+        </is>
+      </c>
+      <c r="AE13" s="6" t="inlineStr">
+        <is>
+          <t>K210A</t>
+        </is>
+      </c>
+      <c r="AF13" s="6" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="AG13" s="6" t="inlineStr">
+        <is>
+          <t>mixed consensus signal: 1 positions, max_minor_allele_fraction=0.300</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr"/>
+      <c r="AI13" s="6" t="inlineStr"/>
+      <c r="AJ13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="n">
+        <v>0.9053</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>5_2</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>A643G, A644C</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>K215A</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="n">
+        <v>0.9566</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr"/>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="n">
+        <v>0.9249000000000001</v>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>6_2</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>C680T</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>A227V</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AJ11" s="4" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['WRONG_AA']). Highest-volume NB02 (304 reads) used as fallback.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>330</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>338</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>330</v>
-      </c>
-      <c r="F12" s="4" t="n">
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="n">
-        <v>0.9617</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>330</v>
-      </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="n">
-        <v>0.9351</v>
-      </c>
-      <c r="AA12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>3_2</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>C613G, A614C</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr">
-        <is>
-          <t>Q205A</t>
-        </is>
-      </c>
-      <c r="AF12" s="4" t="inlineStr">
-        <is>
-          <t>FRAMESHIFT</t>
-        </is>
-      </c>
-      <c r="AG12" s="4" t="inlineStr">
-        <is>
-          <t>consensus net indel 1 bp not divisible by 3 (frameshift)</t>
-        </is>
-      </c>
-      <c r="AH12" s="4" t="inlineStr">
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="n">
+        <v>0.9476</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>7_2</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>A704C</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>D235A</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AI12" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AJ12" s="4" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['FRAMESHIFT']). Highest-volume NB02 (330 reads) used as fallback.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>208</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5" t="inlineStr"/>
-      <c r="S13" s="5" t="n">
-        <v>0.9684</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="U13" s="5" t="inlineStr"/>
-      <c r="V13" s="5" t="inlineStr"/>
-      <c r="W13" s="5" t="inlineStr"/>
-      <c r="X13" s="5" t="inlineStr"/>
-      <c r="Y13" s="5" t="inlineStr"/>
-      <c r="Z13" s="5" t="n">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="5" t="inlineStr"/>
-      <c r="AC13" s="5" t="inlineStr">
-        <is>
-          <t>4_2</t>
-        </is>
-      </c>
-      <c r="AD13" s="5" t="inlineStr">
-        <is>
-          <t>A628G, A629C</t>
-        </is>
-      </c>
-      <c r="AE13" s="5" t="inlineStr">
-        <is>
-          <t>K210A</t>
-        </is>
-      </c>
-      <c r="AF13" s="5" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="AG13" s="5" t="inlineStr">
-        <is>
-          <t>mixed consensus signal: 1 positions, max_minor_allele_fraction=0.300</t>
-        </is>
-      </c>
-      <c r="AH13" s="5" t="inlineStr"/>
-      <c r="AI13" s="5" t="inlineStr"/>
-      <c r="AJ13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>253</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>261</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>253</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="n">
-        <v>0.9414</v>
-      </c>
-      <c r="T14" s="4" t="n">
-        <v>253</v>
-      </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="n">
-        <v>0.9053</v>
-      </c>
-      <c r="AA14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>5_2</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>A625G, G626C, C634G, A643G, A644C, C652G, A653C, C661G, T662C, G663C, T670G, T671C</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t>S209A, P212A, K215A, H218A, L221A, F224A</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>MANY</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>observed 6 AA changes &gt; cutoff 5</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AJ14" s="4" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['MANY']). Highest-volume NB02 (253 reads) used as fallback.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0.966</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="n">
-        <v>0.9566</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="n">
-        <v>0.7219</v>
-      </c>
-      <c r="AA15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr">
-        <is>
-          <t>substitution support 0.722 below plate baseline 0.915 (MAD 0.015)</t>
-        </is>
-      </c>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>6_2</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>C680T</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr">
-        <is>
-          <t>A227V</t>
-        </is>
-      </c>
-      <c r="AF15" s="3" t="inlineStr">
-        <is>
-          <t>LOWDEPTH</t>
-        </is>
-      </c>
-      <c r="AG15" s="3" t="inlineStr">
-        <is>
-          <t>read_count=14 &lt; min_read_count=30</t>
-        </is>
-      </c>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>287</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>295</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>287</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="n">
-        <v>0.9476</v>
-      </c>
-      <c r="T16" s="6" t="n">
-        <v>287</v>
-      </c>
-      <c r="U16" s="6" t="inlineStr"/>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="6" t="inlineStr"/>
-      <c r="Y16" s="6" t="inlineStr"/>
-      <c r="Z16" s="6" t="n">
-        <v>0.9154</v>
-      </c>
-      <c r="AA16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="6" t="inlineStr"/>
-      <c r="AC16" s="6" t="inlineStr">
-        <is>
-          <t>7_2</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr">
-        <is>
-          <t>G4N, T5N, G6N, A7N, G8N, A704C</t>
-        </is>
-      </c>
-      <c r="AE16" s="6" t="inlineStr">
-        <is>
-          <t>D235A</t>
-        </is>
-      </c>
-      <c r="AF16" s="6" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AG16" s="6" t="inlineStr">
-        <is>
-          <t>consensus_n_fraction=0.007 &gt; max_consensus_n_fraction=0.000; no_call_aa=2</t>
-        </is>
-      </c>
-      <c r="AH16" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AI16" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AJ16" s="6" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['NO_CALL']). Highest-volume NB02 (287 reads) used as fallback.</t>
-        </is>
-      </c>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4276,7 +4188,7 @@
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="46" customWidth="1" min="30" max="30"/>
     <col width="42" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
     <col width="46" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -5310,292 +5222,288 @@
       <c r="AJ10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="2" t="n">
         <v>0.97</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="2" t="n">
         <v>174</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>174</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="n">
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="n">
+      <c r="M11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="n">
         <v>0.9873</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="2" t="n">
         <v>174</v>
       </c>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="n">
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="n">
         <v>0.9572000000000001</v>
       </c>
-      <c r="AA11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
+      <c r="AA11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>2_2</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>A599G</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr">
-        <is>
-          <t>H200R</t>
-        </is>
-      </c>
-      <c r="AF11" s="4" t="inlineStr">
-        <is>
-          <t>WRONG_AA</t>
-        </is>
-      </c>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t>expected H200A, observed H200R</t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>C598G, A599C</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>H200A</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="2" t="n">
         <v>179</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="n">
+      <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="n">
         <v>0.9656</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="T12" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="n">
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="n">
         <v>0.9265</v>
       </c>
-      <c r="AA12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AA12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>3_2</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AD12" s="2" t="inlineStr">
         <is>
           <t>C613G, A614C</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AE12" s="2" t="inlineStr">
         <is>
           <t>Q205A</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
-        <is>
-          <t>FRAMESHIFT</t>
-        </is>
-      </c>
-      <c r="AG12" s="4" t="inlineStr">
-        <is>
-          <t>consensus net indel 1 bp not divisible by 3 (frameshift)</t>
-        </is>
-      </c>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="2" t="n">
         <v>0.97</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>208</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="C13" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5" t="inlineStr"/>
-      <c r="S13" s="5" t="n">
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="n">
         <v>0.9586</v>
       </c>
-      <c r="T13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="U13" s="5" t="inlineStr"/>
-      <c r="V13" s="5" t="inlineStr"/>
-      <c r="W13" s="5" t="inlineStr"/>
-      <c r="X13" s="5" t="inlineStr"/>
-      <c r="Y13" s="5" t="inlineStr"/>
-      <c r="Z13" s="5" t="n">
-        <v>0.9213</v>
-      </c>
-      <c r="AA13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="5" t="inlineStr"/>
-      <c r="AC13" s="5" t="inlineStr">
+      <c r="T13" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>4_2</t>
         </is>
       </c>
-      <c r="AD13" s="5" t="inlineStr">
+      <c r="AD13" s="2" t="inlineStr">
         <is>
           <t>A628G, A629C</t>
         </is>
       </c>
-      <c r="AE13" s="5" t="inlineStr">
+      <c r="AE13" s="2" t="inlineStr">
         <is>
           <t>K210A</t>
         </is>
       </c>
-      <c r="AF13" s="5" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="AG13" s="5" t="inlineStr">
-        <is>
-          <t>mixed consensus signal: 1 positions, max_minor_allele_fraction=0.300</t>
-        </is>
-      </c>
-      <c r="AH13" s="5" t="inlineStr"/>
-      <c r="AI13" s="5" t="inlineStr"/>
-      <c r="AJ13" s="5" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -5789,109 +5697,105 @@
           <t>read_count=14 &lt; min_read_count=30</t>
         </is>
       </c>
-      <c r="AH15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
       <c r="AI15" s="3" t="inlineStr"/>
       <c r="AJ15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>0.97</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>163</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>171</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>163</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" t="n">
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="n">
         <v>0.0069</v>
       </c>
-      <c r="J16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6" t="n">
+      <c r="J16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
         <v>0.04</v>
       </c>
-      <c r="M16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="n">
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="n">
         <v>0.9947</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="7" t="n">
         <v>163</v>
       </c>
-      <c r="U16" s="6" t="inlineStr"/>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="6" t="inlineStr"/>
-      <c r="Y16" s="6" t="inlineStr"/>
-      <c r="Z16" s="6" t="n">
+      <c r="U16" s="7" t="inlineStr"/>
+      <c r="V16" s="7" t="inlineStr"/>
+      <c r="W16" s="7" t="inlineStr"/>
+      <c r="X16" s="7" t="inlineStr"/>
+      <c r="Y16" s="7" t="inlineStr"/>
+      <c r="Z16" s="7" t="n">
         <v>0.9675</v>
       </c>
-      <c r="AA16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="6" t="inlineStr"/>
-      <c r="AC16" s="6" t="inlineStr">
+      <c r="AA16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="7" t="inlineStr"/>
+      <c r="AC16" s="7" t="inlineStr">
         <is>
           <t>7_2</t>
         </is>
       </c>
-      <c r="AD16" s="6" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
         <is>
           <t>G4N, T5N, G6N, A7N, G8N, A704C</t>
         </is>
       </c>
-      <c r="AE16" s="6" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
         <is>
           <t>D235A</t>
         </is>
       </c>
-      <c r="AF16" s="6" t="inlineStr">
+      <c r="AF16" s="7" t="inlineStr">
         <is>
           <t>NO_CALL</t>
         </is>
       </c>
-      <c r="AG16" s="6" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>consensus_n_fraction=0.007 &gt; max_consensus_n_fraction=0.000; no_call_aa=2</t>
         </is>
       </c>
-      <c r="AH16" s="6" t="inlineStr"/>
-      <c r="AI16" s="6" t="inlineStr"/>
-      <c r="AJ16" s="6" t="inlineStr"/>
+      <c r="AH16" s="7" t="inlineStr"/>
+      <c r="AI16" s="7" t="inlineStr"/>
+      <c r="AJ16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -6085,14 +5989,14 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -6543,7 +6447,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>NB02</t>
+          <t>NB03</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -6556,33 +6460,21 @@
           <t>H200A</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>WRONG_AA</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['WRONG_AA']). Highest-volume NB02 (304 reads) used as fallback.</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>expected H200A, observed H200R</t>
-        </is>
-      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr"/>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>H200R</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.9414</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>0</v>
@@ -6610,26 +6502,14 @@
           <t>Q205A</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>FRAMESHIFT</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['FRAMESHIFT']). Highest-volume NB02 (330 reads) used as fallback.</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>consensus net indel 1 bp not divisible by 3 (frameshift)</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="10" t="inlineStr"/>
       <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Q205A</t>
@@ -6651,7 +6531,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>NB01</t>
+          <t>NB03</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -6664,33 +6544,21 @@
           <t>K210A</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['MIXED']). Highest-volume NB01 (200 reads) used as fallback.</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>mixed consensus signal: 1 positions, max_minor_allele_fraction=0.300</t>
-        </is>
-      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="10" t="inlineStr"/>
       <c r="I13" s="10" t="inlineStr">
         <is>
           <t>K210A</t>
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.9161</v>
+        <v>0.9192</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>0</v>
@@ -6705,7 +6573,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>NB02</t>
+          <t>NB01</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -6718,33 +6586,21 @@
           <t>K215A</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>MANY</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['MANY']). Highest-volume NB02 (253 reads) used as fallback.</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>observed 6 AA changes &gt; cutoff 5</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr"/>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>S209A, P212A, K215A, H218A, L221A, F224A</t>
+          <t>K215A</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.9053</v>
+        <v>0.949</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>0</v>
@@ -6759,7 +6615,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>NB03</t>
+          <t>NB02</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -6772,34 +6628,26 @@
           <t>A227V</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>LOWDEPTH</t>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr"/>
       <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>read_count=14 &lt; min_read_count=30</t>
-        </is>
-      </c>
+      <c r="H15" s="10" t="inlineStr"/>
       <c r="I15" s="10" t="inlineStr">
         <is>
           <t>A227V</t>
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.7436</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>substitution support 0.744 below plate baseline 0.942 (MAD 0.018)</t>
-        </is>
-      </c>
+      <c r="L15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -6822,26 +6670,14 @@
           <t>D235A</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>All plates below pickable threshold (only ['NO_CALL']). Highest-volume NB02 (287 reads) used as fallback.</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>consensus_n_fraction=0.007 &gt; max_consensus_n_fraction=0.000; no_call_aa=2</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr"/>
       <c r="I16" s="10" t="inlineStr">
         <is>
           <t>D235A</t>
@@ -8406,10 +8242,10 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="46" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
@@ -9132,7 +8968,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>NB02</t>
+          <t>NB03</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -9142,7 +8978,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>H200R</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="G11" s="12" t="n">
@@ -9168,7 +9004,7 @@
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>H200R</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="M11" s="12" t="n">
@@ -9181,7 +9017,7 @@
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9086,7 @@
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9106,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>NB01</t>
+          <t>NB03</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -9284,11 +9120,11 @@
         </is>
       </c>
       <c r="G13" s="12" t="n">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>N=0.000; low_depth=0; low_q=0; mix=1/0.300; drop_mapq=5; drop_span=3</t>
+          <t>N=0.000; low_depth=0; low_q=0; mix=0/0.040; drop_mapq=5; drop_span=3</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -9310,16 +9146,16 @@
         </is>
       </c>
       <c r="M13" s="12" t="n">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
-          <t>N=0.000; low_depth=0; low_q=0; mix=1/0.300; drop_mapq=5; drop_span=3</t>
+          <t>N=0.000; low_depth=0; low_q=0; mix=0/0.040; drop_mapq=5; drop_span=3</t>
         </is>
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9175,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>NB02</t>
+          <t>NB01</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -9349,7 +9185,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>S209A, P212A, K215A, H218A, L221A, F224A</t>
+          <t>K215A</t>
         </is>
       </c>
       <c r="G14" s="10" t="n">
@@ -9362,7 +9198,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>S209A, P212A, K215A, H218A, L221A, F224A</t>
+          <t>K215A</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
@@ -9388,7 +9224,7 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9244,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>NB03</t>
+          <t>NB02</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -9422,7 +9258,7 @@
         </is>
       </c>
       <c r="G15" s="12" t="n">
-        <v>14</v>
+        <v>256</v>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
@@ -9435,7 +9271,7 @@
         </is>
       </c>
       <c r="J15" s="12" t="n">
-        <v>14</v>
+        <v>266</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -9457,7 +9293,7 @@
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9331,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>N=0.007; low_depth=0; low_q=0; mix=0/0.040; drop_mapq=5; drop_span=3</t>
+          <t>N=0.000; low_depth=0; low_q=0; mix=0/0.040; drop_mapq=5; drop_span=3</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -9508,7 +9344,7 @@
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>N=0.007; low_depth=0; low_q=0; mix=0/0.040; drop_mapq=5; drop_span=3</t>
+          <t>N=0.000; low_depth=0; low_q=0; mix=0/0.040; drop_mapq=5; drop_span=3</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
@@ -9526,7 +9362,7 @@
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9529,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -9717,7 +9553,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C21" s="12" t="n"/>
       <c r="D21" s="12" t="n"/>
@@ -10143,12 +9979,20 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>NB02</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr"/>
+          <t>NB03</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -10170,8 +10014,16 @@
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
@@ -10189,12 +10041,20 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>NB01</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr"/>
+          <t>NB03</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -10212,11 +10072,19 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>NB02</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
+          <t>NB01</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
@@ -10235,11 +10103,19 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>NB03</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr"/>
-      <c r="F15" s="12" t="inlineStr"/>
+          <t>NB02</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
@@ -10261,8 +10137,16 @@
           <t>NB02</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
@@ -10377,7 +10261,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>2026-08-31T04:38:48Z</t>
+          <t>2026-08-31T05:28:20Z</t>
         </is>
       </c>
     </row>
